--- a/Result/profitability/6603.xlsx
+++ b/Result/profitability/6603.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,7 +669,7 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13125</v>
+        <v>0.125</v>
       </c>
       <c r="N2" t="n">
         <v>24.285</v>
@@ -780,10 +780,10 @@
         <v>0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.14125</v>
+        <v>0.14875</v>
       </c>
       <c r="N3" t="n">
-        <v>23.63625</v>
+        <v>23.56125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0.16625</v>
+        <v>0.1775</v>
       </c>
       <c r="N4" t="n">
-        <v>22.8275</v>
+        <v>22.94875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.67</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07999999999999997</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>21.01125</v>
+        <v>21.07</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04624999999999998</v>
+        <v>0.02249999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>19.3</v>
+        <v>19.11125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00124999999999998</v>
+        <v>-0.02750000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>18.24625</v>
+        <v>18.2825</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.005000000000000025</v>
+        <v>0.00499999999999997</v>
       </c>
       <c r="N8" t="n">
-        <v>17.84375</v>
+        <v>17.93</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001249999999999975</v>
+        <v>0.001249999999999973</v>
       </c>
       <c r="N9" t="n">
         <v>16.8875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6603</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D75" t="n">
+        <v>900</v>
+      </c>
+      <c r="E75" t="n">
+        <v>305</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>41</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34</v>
+      </c>
+      <c r="K75" t="n">
+        <v>19</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.28125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6900000000000013</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0280146163215591</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.4699999999999989</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01891348088531175</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
